--- a/examples/case_0001/Geometria.xlsx
+++ b/examples/case_0001/Geometria.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\Proyectos python\StructureLab\cases\case_0001\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\Proyectos python\StructureLab\examples\case_0001\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD08EE7B-615A-4B10-BD44-B93C00E63F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E243C0F-BAF6-4142-B346-67573C1D8976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{08B69389-F5AB-430C-A6FC-8A2E5D2BC54C}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{08B69389-F5AB-430C-A6FC-8A2E5D2BC54C}"/>
   </bookViews>
   <sheets>
     <sheet name="Program Control" sheetId="2" r:id="rId1"/>
@@ -375,7 +375,7 @@
     <t>VCIM70X70FC24.5(SM)</t>
   </si>
   <si>
-    <t>VCIM50X50FC28</t>
+    <t>VCIM40X50FC28</t>
   </si>
 </sst>
 </file>
@@ -1214,7 +1214,7 @@
         <v>500</v>
       </c>
       <c r="E5">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>24</v>
